--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,11 +459,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -486,11 +482,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -513,11 +505,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -540,11 +528,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -567,11 +551,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -594,11 +574,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -621,11 +597,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -648,11 +620,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -675,11 +643,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -702,11 +666,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -729,11 +689,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -756,11 +712,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -783,11 +735,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1987,6 +1935,357 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>数通设备安装</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>存储设备安装</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>昇腾服务器安装</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>数通设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>存储设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>昇腾设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>数通设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>存储设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>昇腾设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>使能服务</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AI 计算使能服务</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>数通设备运维服务</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>存储设备运维服务</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>昇腾设备运维服务</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,11 +1954,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -1981,11 +1977,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2008,11 +2000,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2035,11 +2023,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2062,11 +2046,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2089,11 +2069,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2116,11 +2092,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2143,11 +2115,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2170,11 +2138,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2197,11 +2161,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2224,11 +2184,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2251,11 +2207,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2278,14 +2230,361 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>数通设备安装</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>存储设备安装</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>昇腾服务器安装</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>数通设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>存储设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>昇腾设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>数通设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>存储设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>昇腾设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>使能服务</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AI 计算使能服务</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>数通设备运维服务</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>存储设备运维服务</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>昇腾设备运维服务</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务交付界面表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -482,7 +486,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -505,7 +513,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -528,7 +540,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -551,7 +567,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -574,7 +594,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -597,7 +621,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -620,7 +648,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -643,7 +675,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -666,7 +702,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -689,7 +729,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -712,7 +756,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -735,7 +783,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -2253,11 +2305,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2280,11 +2328,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2307,11 +2351,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2334,11 +2374,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2361,11 +2397,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2388,11 +2420,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2415,11 +2443,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2442,11 +2466,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2469,11 +2489,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2496,11 +2512,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2523,11 +2535,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2550,11 +2558,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2577,14 +2581,309 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>数通设备安装</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>存储设备安装</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>昇腾服务器安装</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>数通设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>存储设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>昇腾设备规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>数通设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>存储设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>技术集成服务</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>昇腾设备技术集成服务</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>使能服务</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AI 计算使能服务</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>数通设备运维服务</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>存储设备运维服务</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>运维服务</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>昇腾设备运维服务</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
